--- a/server/apps/cmdb/support-files/model_config.xlsx
+++ b/server/apps/cmdb/support-files/model_config.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="15780" tabRatio="896" firstSheet="40" activeTab="49"/>
+    <workbookView windowHeight="16760" tabRatio="896" firstSheet="43" activeTab="56"/>
   </bookViews>
   <sheets>
     <sheet name="classifications" sheetId="1" r:id="rId1"/>
@@ -206,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13000" uniqueCount="1181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13027" uniqueCount="1184">
   <si>
     <t>模型分类ID</t>
   </si>
@@ -2287,6 +2287,15 @@
   </si>
   <si>
     <t>排除系统进程</t>
+  </si>
+  <si>
+    <t>自动关联规则</t>
+  </si>
+  <si>
+    <t>auto_relation_rule</t>
+  </si>
+  <si>
+    <t>{"rules": [[{"src_field_id": "ip_addr", "dst_field_id": "ip_addr"}]]}</t>
   </si>
   <si>
     <t>1:1</t>
@@ -3763,7 +3772,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3794,6 +3803,13 @@
     </font>
     <font>
       <sz val="11.25"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4323,16 +4339,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
@@ -4341,119 +4354,122 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="5">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="6">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="5">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="7">
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4476,6 +4492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4485,13 +4502,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4503,7 +4520,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -4709,7 +4726,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="中色系标题行镶边行表格样式_6e22f3" count="7" xr9:uid="{BCA94707-2D4E-F656-05A1-D769CAFFBFF3}">
+    <tableStyle name="中色系标题行镶边行表格样式_6e22f3" count="7" xr9:uid="{DD932B45-A296-ED00-88BF-D8696446F0C1}">
       <tableStyleElement type="wholeTable" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="totalRow" dxfId="5"/>
@@ -5022,186 +5039,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="s">
+      <c r="A1" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="21" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="21" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="21" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="21" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="21" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="20" t="s">
+      <c r="A17" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="21" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="21" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="21" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="21" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="20" t="s">
+      <c r="A21" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="21" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="21" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="21" t="s">
         <v>45</v>
       </c>
     </row>
@@ -5891,10 +5908,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -6254,7 +6271,7 @@
         <v>215</v>
       </c>
       <c r="C4" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="D4" t="s">
         <v>411</v>
@@ -7866,7 +7883,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="B3" t="s">
         <v>213</v>
@@ -8456,10 +8473,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>359</v>
@@ -8486,10 +8503,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>359</v>
@@ -8516,10 +8533,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>359</v>
@@ -8546,10 +8563,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>359</v>
@@ -8576,10 +8593,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>359</v>
@@ -9113,10 +9130,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>359</v>
@@ -9772,7 +9789,7 @@
         <v>589</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -9799,10 +9816,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -9859,10 +9876,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -9892,7 +9909,7 @@
         <v>560</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -9922,7 +9939,7 @@
         <v>562</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -9952,7 +9969,7 @@
         <v>361</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -10009,10 +10026,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>324</v>
@@ -10039,10 +10056,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>324</v>
@@ -10069,10 +10086,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>324</v>
@@ -10099,10 +10116,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>324</v>
@@ -10129,10 +10146,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>324</v>
@@ -10665,10 +10682,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -10695,10 +10712,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -10818,7 +10835,7 @@
         <v>589</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -10875,7 +10892,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>564</v>
@@ -10905,10 +10922,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -10938,7 +10955,7 @@
         <v>562</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -10968,7 +10985,7 @@
         <v>335</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -10998,7 +11015,7 @@
         <v>542</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>324</v>
@@ -11025,10 +11042,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>324</v>
@@ -11055,10 +11072,10 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>324</v>
@@ -11085,10 +11102,10 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>324</v>
@@ -11115,10 +11132,10 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>324</v>
@@ -11145,10 +11162,10 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>324</v>
@@ -12095,10 +12112,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -12125,10 +12142,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -12275,10 +12292,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -12308,7 +12325,7 @@
         <v>560</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -12335,10 +12352,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -12428,7 +12445,7 @@
         <v>335</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -12458,7 +12475,7 @@
         <v>542</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>324</v>
@@ -12485,10 +12502,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>324</v>
@@ -12991,10 +13008,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -13021,10 +13038,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -13141,10 +13158,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -13171,10 +13188,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -13201,10 +13218,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -13231,10 +13248,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -13261,10 +13278,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -13291,10 +13308,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -13321,10 +13338,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -13351,10 +13368,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>324</v>
@@ -13857,10 +13874,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -13947,10 +13964,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -13977,10 +13994,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -14007,10 +14024,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -14037,10 +14054,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -14070,7 +14087,7 @@
         <v>595</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -14514,10 +14531,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -14604,10 +14621,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -14634,10 +14651,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -14664,10 +14681,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -14697,7 +14714,7 @@
         <v>595</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -15142,10 +15159,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -15172,10 +15189,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -15202,10 +15219,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -15292,7 +15309,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>601</v>
@@ -15322,7 +15339,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>602</v>
@@ -15415,7 +15432,7 @@
         <v>387</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -15472,10 +15489,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -15980,10 +15997,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -16103,7 +16120,7 @@
         <v>387</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -16133,7 +16150,7 @@
         <v>539</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -16160,10 +16177,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -16190,10 +16207,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -17147,10 +17164,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -17267,10 +17284,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -17327,10 +17344,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>359</v>
@@ -17357,10 +17374,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>359</v>
@@ -17818,10 +17835,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -18844,7 +18861,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -21780,7 +21797,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -22147,7 +22164,7 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -24181,10 +24198,10 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="B3" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C3" t="s">
         <v>438</v>
@@ -25042,10 +25059,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -25502,7 +25519,7 @@
         <v>560</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -25557,10 +25574,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -25589,7 +25606,7 @@
         <v>523</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -25615,10 +25632,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="2" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -25644,10 +25661,10 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -25673,10 +25690,10 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="2" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -25702,10 +25719,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="2" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>324</v>
@@ -26043,10 +26060,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -26072,10 +26089,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -26101,10 +26118,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -26159,10 +26176,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -26954,7 +26971,7 @@
         <v>560</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -26980,10 +26997,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -27009,10 +27026,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -27038,10 +27055,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -27408,10 +27425,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -27807,10 +27824,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -27839,7 +27856,7 @@
         <v>433</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -27865,10 +27882,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -27894,10 +27911,10 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="2" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -27923,10 +27940,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -28322,7 +28339,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>306</v>
@@ -28383,7 +28400,7 @@
         <v>361</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -28409,10 +28426,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -28750,10 +28767,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -29120,10 +29137,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -29152,7 +29169,7 @@
         <v>589</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -29181,7 +29198,7 @@
         <v>560</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -29236,10 +29253,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -29265,10 +29282,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="2" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -29606,10 +29623,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -29635,10 +29652,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -29664,10 +29681,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -29751,10 +29768,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -29783,7 +29800,7 @@
         <v>523</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -29809,10 +29826,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -33793,7 +33810,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>416</v>
@@ -34179,7 +34196,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>490</v>
@@ -34237,7 +34254,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>604</v>
@@ -34608,7 +34625,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>490</v>
@@ -34666,7 +34683,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>604</v>
@@ -34698,7 +34715,7 @@
         <v>537</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -34785,7 +34802,7 @@
         <v>531</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -34811,10 +34828,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="2" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -35692,7 +35709,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>519</v>
@@ -35753,7 +35770,7 @@
         <v>531</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -35779,10 +35796,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -36150,7 +36167,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="2" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>519</v>
@@ -36182,7 +36199,7 @@
         <v>531</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -36208,10 +36225,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -36237,10 +36254,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -36266,10 +36283,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -38054,7 +38071,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>416</v>
@@ -38440,10 +38457,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -38498,10 +38515,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -38530,7 +38547,7 @@
         <v>562</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -38559,7 +38576,7 @@
         <v>579</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>359</v>
@@ -38585,10 +38602,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>359</v>
@@ -38646,7 +38663,7 @@
         <v>542</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>359</v>
@@ -38984,10 +39001,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>1174</v>
+        <v>1177</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1175</v>
+        <v>1178</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -39013,7 +39030,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>512</v>
@@ -39071,10 +39088,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>359</v>
@@ -39103,7 +39120,7 @@
         <v>579</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>359</v>
@@ -39129,10 +39146,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="2" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>359</v>
@@ -39190,7 +39207,7 @@
         <v>542</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>359</v>
@@ -39531,7 +39548,7 @@
         <v>488</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1179</v>
+        <v>1182</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>359</v>
@@ -39560,7 +39577,7 @@
         <v>542</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>359</v>
@@ -39615,7 +39632,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>1180</v>
+        <v>1183</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>487</v>
@@ -39990,7 +40007,7 @@
         <v>579</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>359</v>
@@ -43988,7 +44005,7 @@
       <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="12"/>
+      <c r="E1" s="13"/>
     </row>
     <row r="2" ht="17.65" customHeight="1" spans="1:5">
       <c r="A2" s="2" t="s">
@@ -44003,7 +44020,7 @@
       <c r="D2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="13"/>
+      <c r="E2" s="14"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
@@ -44093,7 +44110,7 @@
       <c r="D8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="13"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
@@ -44123,7 +44140,7 @@
       <c r="D10" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="13"/>
+      <c r="E10" s="14"/>
     </row>
     <row r="11" ht="17.65" customHeight="1" spans="1:5">
       <c r="A11" s="4" t="s">
@@ -44132,7 +44149,7 @@
       <c r="B11" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="14" t="s">
         <v>80</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -44147,7 +44164,7 @@
       <c r="B12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="14" t="s">
         <v>71</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -44162,7 +44179,7 @@
       <c r="B13" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="14" t="s">
         <v>74</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -44177,7 +44194,7 @@
       <c r="B14" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="14" t="s">
         <v>86</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -44192,7 +44209,7 @@
       <c r="B15" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="14" t="s">
         <v>89</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -44207,7 +44224,7 @@
       <c r="B16" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="14" t="s">
         <v>92</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -44222,7 +44239,7 @@
       <c r="B17" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="14" t="s">
         <v>95</v>
       </c>
       <c r="D17" s="4" t="s">
@@ -44397,7 +44414,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="15" t="s">
         <v>131</v>
       </c>
       <c r="B30" s="4" t="s">
@@ -44411,7 +44428,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="14" t="s">
+      <c r="A31" s="15" t="s">
         <v>134</v>
       </c>
       <c r="B31" s="4" t="s">
@@ -44423,7 +44440,7 @@
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="15" t="s">
         <v>136</v>
       </c>
       <c r="B32" s="4" t="s">
@@ -44435,7 +44452,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="14" t="s">
+      <c r="A33" s="15" t="s">
         <v>138</v>
       </c>
       <c r="B33" s="4" t="s">
@@ -44459,7 +44476,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="15" t="s">
         <v>142</v>
       </c>
       <c r="B35" s="4" t="s">
@@ -44483,7 +44500,7 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="16" t="s">
         <v>146</v>
       </c>
       <c r="B37" s="4" t="s">
@@ -44495,7 +44512,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="15" t="s">
         <v>148</v>
       </c>
       <c r="B38" s="4" t="s">
@@ -44507,7 +44524,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="15" t="s">
         <v>150</v>
       </c>
       <c r="B39" s="4" t="s">
@@ -44519,7 +44536,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="15" t="s">
         <v>152</v>
       </c>
       <c r="B40" s="4" t="s">
@@ -44531,7 +44548,7 @@
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="14" t="s">
+      <c r="A41" s="15" t="s">
         <v>154</v>
       </c>
       <c r="B41" s="4" t="s">
@@ -44543,7 +44560,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="15" t="s">
         <v>156</v>
       </c>
       <c r="B42" s="4" t="s">
@@ -44555,7 +44572,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="15" t="s">
         <v>158</v>
       </c>
       <c r="B43" s="4" t="s">
@@ -44567,7 +44584,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="15" t="s">
         <v>160</v>
       </c>
       <c r="B44" s="4" t="s">
@@ -44579,7 +44596,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="16" t="s">
+      <c r="A45" s="17" t="s">
         <v>162</v>
       </c>
       <c r="B45" s="4" t="s">
@@ -44591,7 +44608,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="15" t="s">
         <v>164</v>
       </c>
       <c r="B46" s="4" t="s">
@@ -44603,7 +44620,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="15" t="s">
         <v>166</v>
       </c>
       <c r="B47" s="4" t="s">
@@ -44615,7 +44632,7 @@
       </c>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="15" t="s">
         <v>168</v>
       </c>
       <c r="B48" s="4" t="s">
@@ -44627,7 +44644,7 @@
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="14" t="s">
+      <c r="A49" s="15" t="s">
         <v>170</v>
       </c>
       <c r="B49" s="4" t="s">
@@ -44639,7 +44656,7 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="15" t="s">
         <v>172</v>
       </c>
       <c r="B50" s="4" t="s">
@@ -44651,7 +44668,7 @@
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="16" t="s">
+      <c r="A51" s="17" t="s">
         <v>174</v>
       </c>
       <c r="B51" s="4" t="s">
@@ -44663,7 +44680,7 @@
       </c>
     </row>
     <row r="52" spans="1:4">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="16" t="s">
         <v>176</v>
       </c>
       <c r="B52" s="4" t="s">
@@ -45249,7 +45266,7 @@
       <c r="D100" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E100" s="17"/>
+      <c r="E100" s="18"/>
     </row>
     <row r="101" spans="1:6">
       <c r="A101" s="4" t="s">
@@ -45262,7 +45279,7 @@
       <c r="D101" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E101" s="17"/>
+      <c r="E101" s="18"/>
     </row>
     <row r="102" spans="1:6">
       <c r="A102" s="4" t="s">
@@ -45275,7 +45292,7 @@
       <c r="D102" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E102" s="17"/>
+      <c r="E102" s="18"/>
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="4" t="s">
@@ -45288,8 +45305,8 @@
       <c r="D103" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E103" s="17"/>
-      <c r="F103" s="17"/>
+      <c r="E103" s="18"/>
+      <c r="F103" s="18"/>
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="4" t="s">
@@ -45302,8 +45319,8 @@
       <c r="D104" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E104" s="17"/>
-      <c r="F104" s="17"/>
+      <c r="E104" s="18"/>
+      <c r="F104" s="18"/>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" s="4" t="s">
@@ -45316,8 +45333,8 @@
       <c r="D105" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E105" s="17"/>
-      <c r="F105" s="17"/>
+      <c r="E105" s="18"/>
+      <c r="F105" s="18"/>
     </row>
     <row r="106" spans="1:6">
       <c r="A106" s="4" t="s">
@@ -45330,8 +45347,8 @@
       <c r="D106" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E106" s="17"/>
-      <c r="F106" s="17"/>
+      <c r="E106" s="18"/>
+      <c r="F106" s="18"/>
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="4" t="s">
@@ -45344,8 +45361,8 @@
       <c r="D107" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E107" s="17"/>
-      <c r="F107" s="17"/>
+      <c r="E107" s="18"/>
+      <c r="F107" s="18"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="4" t="s">
@@ -45358,8 +45375,8 @@
       <c r="D108" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E108" s="17"/>
-      <c r="F108" s="17"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="4" t="s">
@@ -45372,8 +45389,8 @@
       <c r="D109" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E109" s="17"/>
-      <c r="F109" s="17"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
     </row>
     <row r="110" spans="1:6">
       <c r="A110" s="4" t="s">
@@ -45386,8 +45403,8 @@
       <c r="D110" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E110" s="17"/>
-      <c r="F110" s="17"/>
+      <c r="E110" s="18"/>
+      <c r="F110" s="18"/>
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="4" t="s">
@@ -46470,7 +46487,7 @@
       <c r="A23" t="s">
         <v>505</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="11" t="s">
         <v>506</v>
       </c>
       <c r="C23" s="2" t="s">
@@ -48449,7 +48466,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>283</v>
       </c>
       <c r="B1" t="s">
@@ -61180,7 +61197,7 @@
       <c r="C21" t="s">
         <v>690</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="10" t="s">
         <v>691</v>
       </c>
       <c r="E21" t="s">
@@ -61378,7 +61395,7 @@
     <col min="2" max="2" width="19.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="18.25" style="1" customWidth="1"/>
+    <col min="5" max="5" width="40.9230769230769" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -61394,7 +61411,9 @@
       <c r="D1" s="7" t="s">
         <v>405</v>
       </c>
-      <c r="E1" s="2"/>
+      <c r="E1" s="8" t="s">
+        <v>693</v>
+      </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
@@ -61412,7 +61431,9 @@
       <c r="D2" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="E2" s="2"/>
+      <c r="E2" s="8" t="s">
+        <v>694</v>
+      </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -61430,7 +61451,9 @@
       <c r="D3" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E3" s="2"/>
+      <c r="E3" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -61448,7 +61471,9 @@
       <c r="D4" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -61466,7 +61491,9 @@
       <c r="D5" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -61484,7 +61511,9 @@
       <c r="D6" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -61502,7 +61531,9 @@
       <c r="D7" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -61520,7 +61551,9 @@
       <c r="D8" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -61538,7 +61571,9 @@
       <c r="D9" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -61556,7 +61591,9 @@
       <c r="D10" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -61574,6 +61611,9 @@
       <c r="D11" s="7" t="s">
         <v>439</v>
       </c>
+      <c r="E11" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -61591,6 +61631,9 @@
       <c r="D12" s="7" t="s">
         <v>439</v>
       </c>
+      <c r="E12" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -61608,6 +61651,9 @@
       <c r="D13" s="7" t="s">
         <v>439</v>
       </c>
+      <c r="E13" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -61625,6 +61671,9 @@
       <c r="D14" s="7" t="s">
         <v>439</v>
       </c>
+      <c r="E14" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -61642,7 +61691,9 @@
       <c r="D15" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
@@ -61660,7 +61711,9 @@
       <c r="D16" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
@@ -61678,7 +61731,9 @@
       <c r="D17" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
@@ -61696,7 +61751,9 @@
       <c r="D18" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
@@ -61714,7 +61771,9 @@
       <c r="D19" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E19" s="2"/>
+      <c r="E19" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
@@ -61732,7 +61791,9 @@
       <c r="D20" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
@@ -61750,7 +61811,9 @@
       <c r="D21" s="7" t="s">
         <v>439</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="8" t="s">
+        <v>695</v>
+      </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
@@ -61768,6 +61831,9 @@
       <c r="D22" s="7" t="s">
         <v>439</v>
       </c>
+      <c r="E22" s="8" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="7" t="s">
@@ -61782,6 +61848,9 @@
       <c r="D23" s="7" t="s">
         <v>439</v>
       </c>
+      <c r="E23" s="8" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="7" t="s">
@@ -61796,6 +61865,9 @@
       <c r="D24" s="7" t="s">
         <v>439</v>
       </c>
+      <c r="E24" s="8" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="7" t="s">
@@ -61810,6 +61882,9 @@
       <c r="D25" s="7" t="s">
         <v>439</v>
       </c>
+      <c r="E25" s="8" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="7" t="s">
@@ -61824,6 +61899,9 @@
       <c r="D26" s="7" t="s">
         <v>439</v>
       </c>
+      <c r="E26" s="8" t="s">
+        <v>695</v>
+      </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="7" t="s">
@@ -61835,8 +61913,11 @@
       <c r="C27" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>693</v>
+      <c r="D27" s="9" t="s">
+        <v>696</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>695</v>
       </c>
     </row>
   </sheetData>
@@ -61921,7 +62002,7 @@
         <v>322</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>324</v>
@@ -61974,10 +62055,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>324</v>
@@ -62006,7 +62087,7 @@
         <v>367</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -62035,7 +62116,7 @@
         <v>351</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>343</v>
@@ -62058,10 +62139,10 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="2" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>343</v>
@@ -62084,10 +62165,10 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>343</v>
@@ -62110,10 +62191,10 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="2" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>343</v>
@@ -62136,10 +62217,10 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -62174,7 +62255,7 @@
         <v>363</v>
       </c>
       <c r="D12" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>326</v>
@@ -62407,7 +62488,7 @@
         <v>322</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>324</v>
@@ -62460,10 +62541,10 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>324</v>
@@ -62570,16 +62651,16 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="2" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>363</v>
       </c>
       <c r="D9" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>326</v>
@@ -63549,7 +63630,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -63606,10 +63687,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -63636,10 +63717,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -63666,10 +63747,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -63696,10 +63777,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -63726,10 +63807,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -63756,10 +63837,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -63786,10 +63867,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -63816,10 +63897,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -63846,10 +63927,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -63876,10 +63957,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -63906,10 +63987,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -63936,10 +64017,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>324</v>
@@ -64420,7 +64501,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -64477,10 +64558,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -64507,10 +64588,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -64537,10 +64618,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -64567,10 +64648,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -64597,10 +64678,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -64627,10 +64708,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -65111,7 +65192,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -65168,10 +65249,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -65198,10 +65279,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -65228,10 +65309,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -65258,10 +65339,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -65288,10 +65369,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -65318,10 +65399,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -65802,7 +65883,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -65859,10 +65940,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -65889,10 +65970,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -65919,10 +66000,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -65949,10 +66030,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -66433,7 +66514,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -66490,10 +66571,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -66520,10 +66601,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -66550,10 +66631,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -66580,10 +66661,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -66610,10 +66691,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -66640,10 +66721,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -66670,10 +66751,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -66700,10 +66781,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -67184,7 +67265,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -67241,10 +67322,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -67271,10 +67352,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -67301,10 +67382,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -67331,10 +67412,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -67361,7 +67442,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>421</v>
@@ -67391,10 +67472,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -67421,10 +67502,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -67451,10 +67532,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -67481,10 +67562,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -67965,7 +68046,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -68022,10 +68103,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -68052,10 +68133,10 @@
     </row>
     <row r="9" ht="17.65" customHeight="1" spans="1:10">
       <c r="A9" s="5" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -68082,10 +68163,10 @@
     </row>
     <row r="10" ht="17.65" customHeight="1" spans="1:10">
       <c r="A10" s="5" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -68112,10 +68193,10 @@
     </row>
     <row r="11" ht="17.65" customHeight="1" spans="1:10">
       <c r="A11" s="5" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -68142,10 +68223,10 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:10">
       <c r="A12" s="5" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -68626,7 +68707,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -68683,10 +68764,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -68713,10 +68794,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -68743,10 +68824,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -68773,10 +68854,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -68803,10 +68884,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -68833,10 +68914,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -68863,10 +68944,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -68893,10 +68974,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -69377,7 +69458,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -69434,10 +69515,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -69464,10 +69545,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -69494,10 +69575,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -69524,10 +69605,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -69554,10 +69635,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -69584,10 +69665,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -69614,10 +69695,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -69644,10 +69725,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -69674,10 +69755,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -69704,10 +69785,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -69734,10 +69815,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -69764,10 +69845,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>324</v>
@@ -69794,10 +69875,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>324</v>
@@ -70278,7 +70359,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -70335,10 +70416,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -70365,10 +70446,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -70395,10 +70476,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -70425,10 +70506,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -70455,10 +70536,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -70485,10 +70566,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -70515,10 +70596,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -70545,10 +70626,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -70575,10 +70656,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -70605,10 +70686,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -70635,10 +70716,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -70665,10 +70746,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>324</v>
@@ -70695,10 +70776,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>324</v>
@@ -71614,7 +71695,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -71671,10 +71752,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -71701,10 +71782,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -71731,10 +71812,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -71761,10 +71842,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -71791,10 +71872,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -71821,10 +71902,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -71851,10 +71932,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -71881,10 +71962,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -72365,7 +72446,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -72422,10 +72503,10 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -72452,10 +72533,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -72482,10 +72563,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -72512,10 +72593,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -72542,10 +72623,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -72572,10 +72653,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -73056,7 +73137,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -73113,10 +73194,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -73143,10 +73224,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -73173,10 +73254,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -73203,10 +73284,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -73233,10 +73314,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -73263,10 +73344,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -73293,10 +73374,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -73777,7 +73858,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -73834,10 +73915,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>757</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>754</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -73864,7 +73945,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>416</v>
@@ -73894,10 +73975,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -73924,10 +74005,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -73954,10 +74035,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -73984,10 +74065,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -74468,7 +74549,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -74525,10 +74606,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -74555,7 +74636,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>538</v>
@@ -74585,10 +74666,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -74615,10 +74696,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -74645,10 +74726,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -74675,10 +74756,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -75159,7 +75240,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -75216,10 +75297,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -75246,10 +75327,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -75276,10 +75357,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -75306,10 +75387,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -75336,10 +75417,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -75366,10 +75447,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -75396,10 +75477,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -75426,10 +75507,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>886</v>
+        <v>889</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -75456,10 +75537,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>887</v>
+        <v>890</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -75486,10 +75567,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>888</v>
+        <v>891</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -75970,7 +76051,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -76027,10 +76108,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>889</v>
+        <v>892</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -76057,10 +76138,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -76087,10 +76168,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -76117,10 +76198,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -76147,10 +76228,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -76177,10 +76258,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -76661,7 +76742,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -76721,7 +76802,7 @@
         <v>288</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -76748,10 +76829,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>897</v>
+        <v>900</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -76778,10 +76859,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -76808,10 +76889,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -76838,10 +76919,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -76868,10 +76949,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -76898,10 +76979,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -76928,10 +77009,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -76958,10 +77039,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>911</v>
+        <v>914</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -76988,10 +77069,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -77472,7 +77553,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -77529,10 +77610,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -77559,10 +77640,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -77589,10 +77670,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -77619,10 +77700,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -77649,10 +77730,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -77679,10 +77760,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -77709,10 +77790,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -77739,10 +77820,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>917</v>
+        <v>920</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>918</v>
+        <v>921</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -77769,10 +77850,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>919</v>
+        <v>922</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -77799,10 +77880,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -77829,10 +77910,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -77859,10 +77940,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>324</v>
@@ -77889,10 +77970,10 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>324</v>
@@ -78373,7 +78454,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -78430,10 +78511,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -78460,10 +78541,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -78490,10 +78571,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>913</v>
+        <v>916</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -78520,10 +78601,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -78550,10 +78631,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -78580,10 +78661,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -78610,10 +78691,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -78640,10 +78721,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -78670,10 +78751,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -78700,10 +78781,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -79300,7 +79381,7 @@
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="10"/>
+      <c r="D10" s="11"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
@@ -79563,7 +79644,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -79620,10 +79701,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -79650,10 +79731,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -79680,10 +79761,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -79710,10 +79791,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -79740,10 +79821,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -79770,10 +79851,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>942</v>
+        <v>945</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>943</v>
+        <v>946</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -79800,10 +79881,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>944</v>
+        <v>947</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -79830,10 +79911,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>945</v>
+        <v>948</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -79860,10 +79941,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>946</v>
+        <v>949</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>947</v>
+        <v>950</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>324</v>
@@ -79890,10 +79971,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>949</v>
+        <v>952</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>324</v>
@@ -79920,10 +80001,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>950</v>
+        <v>953</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>324</v>
@@ -80404,7 +80485,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -80461,10 +80542,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -80491,10 +80572,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -80521,10 +80602,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>914</v>
+        <v>917</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -80551,10 +80632,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>912</v>
+        <v>915</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -80581,10 +80662,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>915</v>
+        <v>918</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -80611,10 +80692,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>916</v>
+        <v>919</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -81095,7 +81176,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -81152,10 +81233,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>951</v>
+        <v>954</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -81182,10 +81263,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>952</v>
+        <v>955</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -81212,10 +81293,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>954</v>
+        <v>957</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -81242,10 +81323,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -81272,10 +81353,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -81302,10 +81383,10 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>955</v>
+        <v>958</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>324</v>
@@ -81332,10 +81413,10 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>957</v>
+        <v>960</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>324</v>
@@ -81362,10 +81443,10 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>958</v>
+        <v>961</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>324</v>
@@ -81846,7 +81927,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -81903,10 +81984,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -81933,10 +82014,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -81963,10 +82044,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -81993,10 +82074,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -82416,10 +82497,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>965</v>
+        <v>968</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>324</v>
@@ -82873,16 +82954,16 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>966</v>
+        <v>969</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>324</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>342</v>
@@ -83355,10 +83436,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>359</v>
@@ -83385,16 +83466,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>363</v>
       </c>
       <c r="D6" t="s">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>326</v>
@@ -83415,16 +83496,16 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>363</v>
       </c>
       <c r="D7" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>326</v>
@@ -84197,10 +84278,10 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>324</v>
@@ -84260,7 +84341,7 @@
         <v>589</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -84287,10 +84368,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -84317,10 +84398,10 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>324</v>
@@ -84347,10 +84428,10 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>324</v>
@@ -84377,10 +84458,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>324</v>
@@ -84407,10 +84488,10 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>324</v>
@@ -84437,10 +84518,10 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>324</v>
@@ -88371,10 +88452,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>324</v>
@@ -88404,7 +88485,7 @@
         <v>531</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>324</v>
@@ -88833,7 +88914,7 @@
         <v>525</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>324</v>
@@ -88890,10 +88971,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>324</v>
@@ -90023,7 +90104,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>485</v>
